--- a/src/main/resources/data/enum_dictionaries.xlsx
+++ b/src/main/resources/data/enum_dictionaries.xlsx
@@ -4,13 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9324" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9324" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="expect_renew_type" sheetId="1" r:id="rId1"/>
     <sheet name="renew_type" sheetId="2" r:id="rId2"/>
     <sheet name="business_class" sheetId="3" r:id="rId3"/>
     <sheet name="order_type" sheetId="4" r:id="rId4"/>
+    <sheet name="businessAction" sheetId="5" r:id="rId5"/>
+    <sheet name="specificItem" sheetId="6" r:id="rId6"/>
+    <sheet name="followResult" sheetId="7" r:id="rId7"/>
+    <sheet name="pay_method" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
   <si>
     <t>code</t>
   </si>
@@ -129,6 +133,111 @@
   </si>
   <si>
     <t>机构自用普通单</t>
+  </si>
+  <si>
+    <t>firstAccess</t>
+  </si>
+  <si>
+    <t>新客户/升版客户首访</t>
+  </si>
+  <si>
+    <t>insAgentSubmissionService</t>
+  </si>
+  <si>
+    <t>代报服务</t>
+  </si>
+  <si>
+    <t>insDayCallOut</t>
+  </si>
+  <si>
+    <t>日常外呼</t>
+  </si>
+  <si>
+    <t>insNotCus</t>
+  </si>
+  <si>
+    <t>新户营销</t>
+  </si>
+  <si>
+    <t>oldTaskExecute-dh</t>
+  </si>
+  <si>
+    <t>任务执行-电话</t>
+  </si>
+  <si>
+    <t>addWxwork</t>
+  </si>
+  <si>
+    <t>企业微信添加</t>
+  </si>
+  <si>
+    <t>agreeRenew</t>
+  </si>
+  <si>
+    <t>同意续费</t>
+  </si>
+  <si>
+    <t>businessConsult</t>
+  </si>
+  <si>
+    <t>业务咨询</t>
+  </si>
+  <si>
+    <t>businessHandling</t>
+  </si>
+  <si>
+    <t>业务办理</t>
+  </si>
+  <si>
+    <t>taxconsult</t>
+  </si>
+  <si>
+    <t>财税业务咨询</t>
+  </si>
+  <si>
+    <t>agreeBuy</t>
+  </si>
+  <si>
+    <t>愿意购买</t>
+  </si>
+  <si>
+    <t>agreeJoinTrain</t>
+  </si>
+  <si>
+    <t>同意参加培训</t>
+  </si>
+  <si>
+    <t>agreeJoinTryout</t>
+  </si>
+  <si>
+    <t>同意试用产品</t>
+  </si>
+  <si>
+    <t>needfollowagain</t>
+  </si>
+  <si>
+    <t>还需再次跟进</t>
+  </si>
+  <si>
+    <t>qwsazxm</t>
+  </si>
+  <si>
+    <t>不认可价值</t>
+  </si>
+  <si>
+    <t>汇款转账</t>
+  </si>
+  <si>
+    <t>微信支付</t>
+  </si>
+  <si>
+    <t>现金</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>通联转账</t>
   </si>
 </sst>
 </file>
@@ -141,9 +250,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -614,138 +731,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1063,13 +1183,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="13.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1125,12 +1246,16 @@
   <sheetPr/>
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="13.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="10.4444444444444" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1178,12 +1303,16 @@
   <sheetPr/>
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="10.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="12.3333333333333" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1239,12 +1368,15 @@
   <sheetPr/>
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="2" width="15.7777777777778" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1270,6 +1402,262 @@
       </c>
       <c r="B4" t="s">
         <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="26.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="29.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="17.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="22.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="23.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="28.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="15.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="14.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
